--- a/www/download/COUNTRY.AUS.rpPE.xlsx
+++ b/www/download/COUNTRY.AUS.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Austrália</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>1.34861762852899</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1.27722079147051</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1.34397767838582</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>1.58881470938095</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>1.54959474777291</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1.71718034717616</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1.93184453411697</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1.83857323206392</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1.53402461090105</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>1.35762575875635</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>1.30917466172452</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1.32740422194791</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1.19252052377757</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>1.16922821167204</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>1.26373683937823</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.289</t>
+          <t>-0.0747582006515491</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.355</t>
+          <t>-0.156717635696669</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.477</t>
+          <t>-0.160852562312858</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.642</t>
+          <t>-0.0331840068070641</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.834</t>
+          <t>-0.0538700861594689</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.012</t>
+          <t>0.0219545631392239</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>0.0675150637024735</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.367</t>
+          <t>0.017976887594443</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9.519</t>
+          <t>-0.146788264114035</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.774</t>
+          <t>-0.227764352868932</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10.029</t>
+          <t>-0.258568691286812</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.288</t>
+          <t>-0.262933269629239</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10.558</t>
+          <t>-0.303294169917029</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>10.861</t>
+          <t>-0.270294078076372</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>10.935</t>
+          <t>-0.239657310910418</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.001</t>
+          <t>-0.40909134023827</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.121</t>
+          <t>-0.461634208446697</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.199</t>
+          <t>-0.46117755084837</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7.404</t>
+          <t>-0.386083298458668</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.566</t>
+          <t>-0.392261425830453</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.737</t>
+          <t>-0.355180883267561</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7.864</t>
+          <t>-0.321119749356741</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.082</t>
+          <t>-0.359178437154741</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8.252</t>
+          <t>-0.458573997540574</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>-0.496544897737119</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>8.741</t>
+          <t>-0.508419550357012</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8.965</t>
+          <t>-0.51425138477935</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>9.202</t>
+          <t>-0.538441043004989</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>9.942</t>
+          <t>-0.511467779505932</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10.452</t>
+          <t>-0.499555011356784</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15262.516</t>
+          <t>-0.755388010499236</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15313.314</t>
+          <t>-0.774277493179727</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15492.621</t>
+          <t>-0.775604515427749</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15809.188</t>
+          <t>-0.756498974407135</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16175.072</t>
+          <t>-0.76682284005554</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16516.061</t>
+          <t>-0.762174879219015</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16578.653</t>
+          <t>-0.750450442990533</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16907.067</t>
+          <t>-0.763872370595999</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17174.77</t>
+          <t>-0.782259709046344</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17645.28</t>
+          <t>-0.807593235078863</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>18026.47</t>
+          <t>-0.808623128935348</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18424.644</t>
+          <t>-0.805651563003364</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>18919.606</t>
+          <t>-0.804324656614958</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20488.035</t>
+          <t>-0.784266588776933</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>21545.023</t>
+          <t>-0.779926028618495</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12828.687</t>
+          <t>50941626567.6593</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12974.476</t>
+          <t>51720052807.8465</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13053.68</t>
+          <t>52258063269.4126</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13459.16</t>
+          <t>55302841953.8622</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13759.368</t>
+          <t>60497200343.1611</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14064.941</t>
+          <t>62014833288.996</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14063.118</t>
+          <t>60970525560.2388</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14373.529</t>
+          <t>64121038772.9884</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14680.712</t>
+          <t>62003920558.2451</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15143.81</t>
+          <t>71861644562.1808</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>15580.662</t>
+          <t>72701926479.61</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15917.851</t>
+          <t>72587424053.0337</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16341.758</t>
+          <t>71854394416.0264</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>17671.991</t>
+          <t>72539402363.0848</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>18590.196</t>
+          <t>75175777131.5601</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>65336916566.009</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>71851620078.593</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>73188081826.291</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>69817489743.2766</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>74755074250.9876</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>75061418527.6929</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>72056849764.6633</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>77794164623.5488</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>86217996075.9169</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>101319025046.298</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>105239187923.182</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>105474050609.47</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>107059959281.154</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>105015576550.515</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>108296915991.675</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>3092097.51794856</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>2893940.49201627</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>2908032.83571635</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>3437890.39043318</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>3629664.71266894</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>3912923.12562945</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>4111948.7658552</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>3851671.89478015</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>2902379.05361064</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>2776954.57122267</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>2511123.00167512</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>2365444.10641915</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>1969865.70614899</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>1801133.16201298</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>1902121.07302464</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>43.91</t>
+          <t>82258.5369991162</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>82927.9646355144</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>83426.3094777427</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>85645.4242224099</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>90879.4537667787</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>94968.9396737349</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>92806.9749183511</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>97030.1128115241</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>106017.883447389</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>115990.685307166</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>127259.137666632</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>135875.499861785</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>154733.81311373</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>180404.869941726</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>176018.507149945</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>168078.083403275</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>172625.265106987</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>170647.841906956</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>171332.704048245</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>189746.575312446</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>189233.933724555</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>179465.841829906</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>193779.184735759</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>217242.922028606</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>261553.817455386</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>286708.627896018</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>304388.973987529</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>356161.710725031</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>408541.055922305</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>390011.564014018</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>-0.468335558077739</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>-0.509546548569383</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>-0.505417152489045</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>-0.43205257950582</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>44.72</t>
+          <t>-0.438643999073211</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>44.39</t>
+          <t>-0.395404749458206</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>-0.358988204831643</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>-0.3834895897025</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>-0.469994176866503</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>-0.515200266913774</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>-0.525433320573028</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>-0.528202792928823</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>-0.550176620030907</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>-0.523490946376089</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>-0.507674440079808</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>74031.509210943</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>79198.3107193253</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>85099.8371356917</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>75727.8216919794</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>81729.8547073177</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>81314.1176749028</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>73193.7582518738</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>76607.355863452</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>90572.4282288111</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>106576.139143213</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>117410.901612856</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>121206.247196359</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>139013.420886207</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>156046.444909782</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>153811.901354841</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.34861762852899</t>
+          <t>9332.7586239615</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.27722079147051</t>
+          <t>10090.3859227324</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.34397767838582</t>
+          <t>10166.3739412701</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.58881470938095</t>
+          <t>9429.34855111089</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.54959474777291</t>
+          <t>9880.45451644738</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.71718034717616</t>
+          <t>9701.85503067478</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.93184453411697</t>
+          <t>9162.73533755844</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.83857323206392</t>
+          <t>9625.28664469569</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.53402461090105</t>
+          <t>10448.6339507143</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.35762575875635</t>
+          <t>11947.8112702526</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.30917466172452</t>
+          <t>12039.8046918122</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.32740422194791</t>
+          <t>11765.1316568603</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.19252052377757</t>
+          <t>11634.1313912984</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.16922821167204</t>
+          <t>10562.7337730197</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.26373683937823</t>
+          <t>10361.55887199</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>20491786524.7654</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>22416395402.4106</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>20352467671.5501</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>20100015601.4859</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>24353128413.4379</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>27614457845.919</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>26588656480.8728</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>26882673602.6759</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>27521926848.1189</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>36883452316.8607</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>41160093361.4316</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>40148529589.7173</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>40246656390.4755</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>43482929159.5995</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>42551773499.1989</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>21274030248.5636</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>22980579642.5854</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>21332948005.8073</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>20859547019.4986</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>24614796286.3281</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>27370048503.47</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>26437084274.62</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>26670057074.6504</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>26772893765.7874</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>36210659050.2724</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>40382838805.0417</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>39585930756.9543</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>40129355371.1738</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>42746914793.6497</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>41970807213.1335</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>-782243723.798176</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-564184240.174841</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-980480334.257128</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.283</t>
+          <t>-759531418.012755</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>-261667872.890172</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>244409342.449075</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>151572206.252876</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>212616528.02548</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>749033082.331503</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.727</t>
+          <t>672793266.588289</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>777254556.389905</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.907</t>
+          <t>562598832.763023</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.169</t>
+          <t>117301019.301697</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>736014365.949816</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>580966286.065405</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>4961.89590540366</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>4948.86460207103</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>5028.11417273451</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>5355.37418654397</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>5546.45243469193</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>5865.69547299098</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>5873.42142738088</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>5934.08941855239</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>5537.83683766895</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>5792.29571478307</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>5713.69013354257</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>5550.75625653136</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.821</t>
+          <t>5233.30430543836</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>5033.23827386295</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>5101.26027329849</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>5871.59889673506</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>5829.65241890502</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>5929.60958741497</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>6346.2703929756</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>6557.46979485182</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>6959.25849353731</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>6965.34277587235</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>7025.93265728576</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>6521.42363278121</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>6791.26817771179</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>6663.96963281004</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>6477.299054996</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>6075.65915209711</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6088.92733997141</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>6402.38072739477</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>73925.3026335695</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>83143.7064783355</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-16.09</t>
+          <t>85657.6703586451</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>71546.4198589818</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>82657.7304240136</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>90273.7457606642</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>80344.7016223961</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>82430.8733489279</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-14.68</t>
+          <t>95572.9106667517</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-22.78</t>
+          <t>122754.293079389</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-25.86</t>
+          <t>149343.211598088</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-26.29</t>
+          <t>161914.494992754</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-30.33</t>
+          <t>195359.198755723</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-27.03</t>
+          <t>243242.166032765</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>200696.483372384</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>7519676770.37844</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>7977231535.40155</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-46.12</t>
+          <t>8198364452.29448</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>7915900357.62167</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>9469327757.44494</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>10599020419.6142</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>9871957675.66219</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-35.92</t>
+          <t>9730901332.21394</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-45.86</t>
+          <t>8549570975.19619</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-49.65</t>
+          <t>10218125644.6361</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-50.84</t>
+          <t>10825776226.4891</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-51.43</t>
+          <t>11091699178.2463</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-53.84</t>
+          <t>11290067389.4642</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-51.15</t>
+          <t>12525059463.1573</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-49.96</t>
+          <t>10666299572.4286</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-75.54</t>
+          <t>70489.1347399083</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-77.43</t>
+          <t>76231.1768153268</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>82714.6367266814</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-75.65</t>
+          <t>74824.5762535685</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-76.68</t>
+          <t>85369.6177766899</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.22</t>
+          <t>83571.7943769528</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-75.05</t>
+          <t>75165.02782931</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-76.39</t>
+          <t>85725.6938519204</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-78.23</t>
+          <t>103238.447633734</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-80.76</t>
+          <t>131595.583649302</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-80.86</t>
+          <t>151441.704391143</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-80.57</t>
+          <t>161775.145211455</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-80.43</t>
+          <t>203614.145602268</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-78.43</t>
+          <t>223979.504872329</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-77.99</t>
+          <t>192821.087558172</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>48668.626</t>
+          <t>26686793641.4119</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48704.123</t>
+          <t>27820293766.5444</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50265.152</t>
+          <t>27527431243.0528</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>54842.025</t>
+          <t>29282279168.9755</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>57925.672</t>
+          <t>34933858251.408</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>62717.968</t>
+          <t>35310808065.3008</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>63590.52</t>
+          <t>34085940040.8953</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>65811.229</t>
+          <t>38099640441.004</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>62076.326</t>
+          <t>39082160091.5646</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>66376.126</t>
+          <t>50464465228.2319</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>66832.124</t>
+          <t>52714656967.0007</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>66639.237</t>
+          <t>51196733918.9458</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>64149.252</t>
+          <t>53700929098.2237</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>66133.135</t>
+          <t>51618816662.1374</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>70012.727</t>
+          <t>51209019587.6493</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>34737.315</t>
+          <t>3436.16789366122</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>35239.875</t>
+          <t>6912.52966300878</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>36197.57</t>
+          <t>2943.03363196362</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>39652.663</t>
+          <t>-3278.15639458673</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>41964.21</t>
+          <t>-2711.88735267633</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45381.777</t>
+          <t>6701.95138371143</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>46189.291</t>
+          <t>5179.67379308611</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>47960.912</t>
+          <t>-3294.82050299244</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>45696.04</t>
+          <t>-7665.53696698253</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>49119.436</t>
+          <t>-8841.29056991314</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>49943.012</t>
+          <t>-2098.49279305482</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>49762.362</t>
+          <t>139.349781299291</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>48158.073</t>
+          <t>-8254.9468465452</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>50040.873</t>
+          <t>19262.6611604358</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>53317.34</t>
+          <t>7875.39581421205</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>50941.627</t>
+          <t>-19167116871.0335</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51720.053</t>
+          <t>-19843062231.1429</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>52258.063</t>
+          <t>-19329066790.7583</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>55302.842</t>
+          <t>-21366378811.3538</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>60497.2</t>
+          <t>-25464530493.963</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>62014.833</t>
+          <t>-24711787645.6866</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>60970.526</t>
+          <t>-24213982365.2331</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>64121.039</t>
+          <t>-28368739108.7901</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>62003.921</t>
+          <t>-30532589116.3684</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>71861.645</t>
+          <t>-40246339583.5958</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>72701.926</t>
+          <t>-41888880740.5116</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>72587.424</t>
+          <t>-40105034740.6995</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>71854.394</t>
+          <t>-42410861708.7594</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>72539.402</t>
+          <t>-39093757198.9801</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>75175.777</t>
+          <t>-40542720015.2207</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>163327.24381</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>178191.58657</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>177514.85328</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>156770.95752</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>169037.74314</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>161160.70924</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>153651.59963</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>169217.48267</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>218098.91304</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>268298.36943</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>308739.17335</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>326150.75571</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>387434.68136</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>426399.06147</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>431019.08545</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24931.172</t>
+          <t>0.0370328827118346</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24845.95</t>
+          <t>0.0412947930615338</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25547.92</t>
+          <t>0.0428288174215696</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>27644.666</t>
+          <t>0.0444688691063616</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>28975.24</t>
+          <t>0.0484719947053628</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>31122.763</t>
+          <t>0.0456376454920952</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>31529.621</t>
+          <t>0.055740460686857</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>32107.017</t>
+          <t>0.062690482003955</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30258.866</t>
+          <t>0.0745508024174448</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>31868.322</t>
+          <t>0.0785655204106469</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>32269.641</t>
+          <t>0.0846975534192888</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>32402.135</t>
+          <t>0.0878669519602035</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>31217.012</t>
+          <t>0.0965892638355247</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>32032.182</t>
+          <t>0.0970063354437479</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>33928.04</t>
+          <t>0.100361075594903</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>189868.494299314</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>213941.082808452</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>211949.947596942</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>190483.508639969</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>205915.128769095</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>197591.943818719</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>184329.016168008</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>204239.350027981</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>260832.844519709</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>317552.901824903</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>354812.091731048</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>383147.040357706</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>462040.19248977</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>511098.123781348</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>498689.56142909</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>65336.917</t>
+          <t>221153.72516354</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>71851.62</t>
+          <t>247042.561166084</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>73188.082</t>
+          <t>245212.233573625</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69817.49</t>
+          <t>218661.70000032</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>74755.074</t>
+          <t>236203.455246225</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>75061.419</t>
+          <t>226529.411581485</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>72056.85</t>
+          <t>211426.463917418</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77794.165</t>
+          <t>234743.684481662</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>86217.996</t>
+          <t>298459.503014282</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>101319.025</t>
+          <t>362225.598050155</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>105239.188</t>
+          <t>401895.913603307</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>105474.051</t>
+          <t>434454.075255592</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>107059.959</t>
+          <t>525383.13595245</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>105015.577</t>
+          <t>581746.34502725</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>108296.916</t>
+          <t>567463.067505893</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>1538087.02899907</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-50.95</t>
+          <t>1590164.74926371</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>1500355.89328043</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-43.21</t>
+          <t>1283312.26438895</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>1330856.39715423</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-39.54</t>
+          <t>1269664.39282344</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-35.9</t>
+          <t>1132604.27923937</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>1202551.23465361</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-47</t>
+          <t>1469065.97468466</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-51.52</t>
+          <t>1726600.80144075</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-52.54</t>
+          <t>1855848.27386571</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-52.82</t>
+          <t>1907051.14573615</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-55.02</t>
+          <t>2169376.54425187</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-52.35</t>
+          <t>2388624.46234074</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-50.77</t>
+          <t>2294004.94937459</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.092</t>
+          <t>221153.72516354</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.894</t>
+          <t>230599.404506205</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.908</t>
+          <t>237949.153674314</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.438</t>
+          <t>250262.060632838</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>258406.949753336</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.913</t>
+          <t>266933.464059074</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.112</t>
+          <t>271889.799504023</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.852</t>
+          <t>278369.726039547</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.902</t>
+          <t>283092.560448583</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.777</t>
+          <t>293634.41830284</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.511</t>
+          <t>304609.966543906</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>316215.071145613</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>330465.34834293</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.801</t>
+          <t>343645.299165299</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.902</t>
+          <t>349635.715183621</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>189868.494299314</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>199357.59835537</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>204863.833201284</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>217116.193006002</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>224556.335046558</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>232338.016803165</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>236773.447442399</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>241378.895999344</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>246305.587297869</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>256072.998226462</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>266920.936391972</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>276821.926296917</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>288651.609567658</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>299855.339807324</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>304287.653401073</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>130991.30575646</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>144863.834973916</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>149358.305756375</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>132795.26679968</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>146239.118943776</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>139258.611128515</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>136325.642552582</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>151995.872398338</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>200092.475445718</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>242227.429649845</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>274596.709926693</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>288773.018604408</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>348551.90427755</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>387758.15075275</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>384040.705494107</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>34737315282.9885</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>35239875058.4274</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>36197569913.5118</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>39652663205.0728</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>41964209530.5196</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>45381777140.7729</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>46189290621.8234</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>47960912350.8154</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>45696039979.137</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>49119436299.0018</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>49943011958.2955</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>49762362496.032</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>48158072743.202</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>50040872997.8552</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>53317339803.2315</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>48668626367.2355</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>48704122616.3629</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>50265152232.277</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>54842025421.9938</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>57925671731.6153</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>62717967539.2776</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>63590520411.937</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>65811228621.8257</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>62076325584.0698</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>66376126160.7884</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>66832124207.1219</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>66639236945.3067</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>64149252038.5666</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>66133134863.0913</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>70012727075.0195</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>24931172398.943</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>24845950026.7115</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>25547919682.4449</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>27644665892.3313</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>28975239803.6837</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>31122763478.9434</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>31529621340.3706</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>32107017243.4628</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>30258865797.062</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>31868322478.1802</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>32269640918.7014</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>32402134668.943</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>31217012110.4157</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>32032181978.4291</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>33928040308.2064</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8288820</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8354550</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>8476975</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8641615</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8833540</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9012162.372977</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9129560.80671462</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9366902.84863187</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9518830.40875171</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9773745.40717266</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>10028875.8637305</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>10288121.0794038</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10558402.0486772</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10861212.6850247</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>10935420.7530093</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7000815</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>7120800</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>7199035</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>7404275</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>7565955</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>7736810.98</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7864119.95</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>8082269.91</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>8251604.61</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>8480132.7</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>8740938.13122661</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>8964969.8520771</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>9202230.54737272</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>9942083.06364353</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>10451797.5846695</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>15262515700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>15313313900</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>15492620800</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>15809187500</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>16175072100</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>16516060800</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16578652800</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>16907066600</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>17174769880</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17645279900</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>18026470142.4781</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>18424644486.6276</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>18919606150.8565</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>20488034752.5043</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>21545022822.5012</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>12828686900</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>12974476100</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13053680400</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13459159500</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>13759368400</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>14064941400</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>14063117500</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>14373529200</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>14680711620</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>15143809500</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>15580661526.7842</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>15917851279.2693</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16341757580.232</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>17671991252.385</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>18590195705.1333</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153864968584301</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.16029700854778</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.166954385727705</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.173855008300376</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.181019712145316</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.188472308501638</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.196239816083751</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.204603232753246</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.210571051646447</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.209717359901643</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.209299821497889</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.37847368190924</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.378806594382501</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.379326311097916</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.380031673104945</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.380924411145202</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.382009092927736</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.383293158770534</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.381499114359128</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.380542432698167</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.392477390240563</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.404215425231224</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.439089920935031</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.43232496849829</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.425147874602951</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.41754189002325</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.409484448138053</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.400947169999198</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.391895596574286</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.385326224316197</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.380315087083958</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.369233821286366</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.357913324699458</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.284043733074465</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.29630641524427</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.309062988716524</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.326005132445565</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.33872832971529</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.35415057198161</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.365081321216332</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.37343063315043</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.372804119651297</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.366926551257351</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.357664758889467</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.355848697211814</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.349388815167077</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.345337483033314</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.348632422905777</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.464279231448657</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.456329998694853</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.451568568218632</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.449268730461982</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.447229005490679</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.443910519470523</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.440169407457856</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.433915692529417</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.42348566409138</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.441693523960817</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.453736060275888</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.451428220209313</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.448850642639693</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.44657341814401</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.444692000641331</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.22310560690545</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.218792157489448</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.210797014493416</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.196154708521024</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.185471236222602</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.173367479976438</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.166177842754383</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.164082245748724</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.175138787685894</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.162808496210403</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.160027752263217</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.164151654007444</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.173189113621801</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.179517670251248</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.178104147881464</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>752494.98168</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>829399.27125</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>832678.26478</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>752129.87266</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>815120.20972</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>781105.49249</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>735918.42278</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>818548.85189</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1043916.75928</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1274561.85401</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1413363.26662</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1511399.28909</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1821221.24465</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2017526.35779</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1968895.58857</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>352145.03092</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>391906.39614</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>394570.53933</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>351456.9668</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>382442.57419</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>365788.02271</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>347752.10647</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>386739.55688</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>498551.97846</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>604453.0277</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>676492.62353</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>723227.09386</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>873935.04023</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>969504.49578</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>951503.773</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2074291.31844027</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2058486.2850259</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2058015.25273273</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2067393.1610367</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2094191.92939219</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2109019.69877836</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2139196.35186379</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2199026.60809042</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2286993.16578155</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2403523.49034269</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2553520.13918935</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2731277.7005298</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2980149.29532968</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3230346.10392524</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3478011.97184729</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
